--- a/Sheets/One-Shot Premades/Vigilante.xlsx
+++ b/Sheets/One-Shot Premades/Vigilante.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Javier\TTRPGs\Marvel Multiverse\Sheets\One-Shot Premades\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Javier\TTRPGs\Marvel Multiverse RPG\Sheets\One-Shot Premades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D7BA26-CCD6-458C-98DA-66549C4CB731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585C3D98-CCCD-44A5-8124-1685C5690174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -262,22 +262,13 @@
     </r>
   </si>
   <si>
-    <t>Luchador (Permanente)</t>
-  </si>
-  <si>
     <t>Postura de Defensa (Estándar o Movimiento, Concentración, 5 Foco)</t>
   </si>
   <si>
     <t>Ataque de Agilidad vs Defensa de Melé a alcance normal. En un éxito, daño normal. Si es Fantástico, doble daño y el objetivo esta Tumbado.</t>
   </si>
   <si>
-    <t>Patada Rápida (Estándar, Instantáneo, 5 Foco)</t>
-  </si>
-  <si>
     <t>Vigilante - Centinela</t>
-  </si>
-  <si>
-    <t>Contraataque (Reacción, Instantáneo, 5 Foco)</t>
   </si>
   <si>
     <t>Vigilante - Acróbata</t>
@@ -319,9 +310,6 @@
     </r>
   </si>
   <si>
-    <t>Ataques vs tus Defensas Físicas tienen Desventaja.</t>
-  </si>
-  <si>
     <t>Básico</t>
   </si>
   <si>
@@ -489,10 +477,22 @@
     <t>Cuanto te atacan vs Defensa Melé. El ataque tiene Desventaja.</t>
   </si>
   <si>
-    <t>Cuanto te atacan vs Defensa Melé. Ataque de Melé vs Defensa de Melé a alcance normal al enemigo que te ataco. En un éxito, daño normal. Si es Fantástico, doble daño y aplica el efecto del Arma.</t>
-  </si>
-  <si>
-    <t>Puedes reemplazar tu Defensa de Agilidad por tu Defensa de Melé.</t>
+    <t>Contraataque (Reacción, Instantáneo)</t>
+  </si>
+  <si>
+    <t>Cuanto te atacan vs Defensa Melé, y el ataque falla. Ataque de Melé vs Defensa de Melé a alcance normal al enemigo que te ataco. En un éxito, daño normal. Si es Fantástico, doble daño y aplica el efecto del Arma.</t>
+  </si>
+  <si>
+    <t>Reemplazas tu Defensa de Agilidad por tu Defensa de Melé.</t>
+  </si>
+  <si>
+    <t>Patada Rápida (Estándar, Instantáneo)</t>
+  </si>
+  <si>
+    <t>Luchador (Estándar o Movimiento, Concentración)</t>
+  </si>
+  <si>
+    <t>El primer ataque vs tu Defensa de Melé o Agilidad que recibes en cada turno tiene Desventaja.</t>
   </si>
 </sst>
 </file>
@@ -2575,7 +2575,7 @@
       <c r="H5" s="98"/>
       <c r="I5" s="99"/>
       <c r="K5" s="58" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L5" s="41"/>
       <c r="M5" s="37"/>
@@ -2648,7 +2648,7 @@
     </row>
     <row r="10" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="70" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B10" s="71"/>
       <c r="C10" s="71"/>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="11" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="74" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B11" s="75"/>
       <c r="C11" s="75"/>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="14" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="70" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B14" s="71"/>
       <c r="C14" s="71"/>
@@ -2733,7 +2733,7 @@
     </row>
     <row r="15" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="74" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B15" s="75"/>
       <c r="C15" s="75"/>
@@ -2752,7 +2752,7 @@
       <c r="B16" s="107"/>
       <c r="C16" s="154" t="str">
         <f>_xlfn.CONCAT("/",IF(A34=0,20,20 + A34 * IF(Modifiers!O6,Modifiers!O6,20)) + Modifiers!N6)</f>
-        <v>/40</v>
+        <v>/20</v>
       </c>
       <c r="D16" s="155"/>
       <c r="E16" s="31"/>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="18" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="70" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B18" s="71"/>
       <c r="C18" s="73"/>
@@ -2798,7 +2798,7 @@
     </row>
     <row r="19" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="136" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B19" s="137"/>
       <c r="C19" s="138"/>
@@ -2821,7 +2821,7 @@
       <c r="D20" s="134"/>
       <c r="E20" s="32" t="str">
         <f>_xlfn.CONCAT("+",IF(Modifiers!K6="Edge",_xlfn.CONCAT(A34,"E"),A34))</f>
-        <v>+1</v>
+        <v>+0</v>
       </c>
       <c r="F20" s="30"/>
       <c r="G20" s="86"/>
@@ -2833,7 +2833,7 @@
     </row>
     <row r="21" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="126" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B21" s="127"/>
       <c r="C21" s="127"/>
@@ -2886,7 +2886,7 @@
       <c r="E24" s="30"/>
       <c r="F24" s="30"/>
       <c r="G24" s="44" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H24" s="45"/>
       <c r="I24" s="39" t="s">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="H27" s="47"/>
       <c r="I27" s="139" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J27" s="139"/>
       <c r="K27" s="139"/>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="H30" s="47"/>
       <c r="I30" s="139" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J30" s="139"/>
       <c r="K30" s="139"/>
@@ -3069,13 +3069,13 @@
     </row>
     <row r="34" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B34" s="118"/>
       <c r="C34" s="119"/>
       <c r="D34" s="120">
         <f xml:space="preserve"> 10 + A34 + Modifiers!B6</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E34" s="121"/>
       <c r="F34" s="30"/>
@@ -3143,13 +3143,13 @@
     </row>
     <row r="38" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" s="145"/>
       <c r="C38" s="121"/>
       <c r="D38" s="120">
         <f xml:space="preserve"> 10 + A38 + Modifiers!B8</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E38" s="121"/>
       <c r="F38" s="30"/>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E48" s="163">
         <f>A38</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="30"/>
       <c r="G48" s="86"/>
@@ -3399,7 +3399,7 @@
     </row>
     <row r="51" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="70" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B51" s="71"/>
       <c r="C51" s="71"/>
@@ -3416,7 +3416,7 @@
     </row>
     <row r="52" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="74" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B52" s="75"/>
       <c r="C52" s="75"/>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D53" s="155"/>
       <c r="E53" s="54" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F53" s="30"/>
       <c r="G53" s="177"/>
@@ -3590,7 +3590,7 @@
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="218" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B2" s="219"/>
       <c r="C2" s="219"/>
@@ -3658,7 +3658,7 @@
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="59" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B8" s="56"/>
       <c r="C8" s="56"/>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B9" s="67"/>
       <c r="C9" s="67"/>
@@ -3684,7 +3684,7 @@
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B10" s="67"/>
       <c r="C10" s="67"/>
@@ -3719,7 +3719,7 @@
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="209" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B13" s="210"/>
       <c r="C13" s="210"/>
@@ -3732,7 +3732,7 @@
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="206" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B14" s="207"/>
       <c r="C14" s="207"/>
@@ -3782,7 +3782,7 @@
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="209" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B18" s="210"/>
       <c r="C18" s="210"/>
@@ -3795,7 +3795,7 @@
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="206" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B19" s="207"/>
       <c r="C19" s="207"/>
@@ -3808,7 +3808,7 @@
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="209" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B20" s="210"/>
       <c r="C20" s="210"/>
@@ -4164,13 +4164,13 @@
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="221" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B1" s="222"/>
       <c r="C1" s="222"/>
       <c r="D1" s="223"/>
       <c r="E1" s="236" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F1" s="237"/>
     </row>
@@ -4215,7 +4215,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="60" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B5" s="61"/>
       <c r="C5" s="61"/>
@@ -4241,7 +4241,7 @@
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="64" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="B7" s="56"/>
       <c r="C7" s="56"/>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="206" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B8" s="207"/>
       <c r="C8" s="207"/>
@@ -4278,7 +4278,7 @@
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="230" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="B10" s="231"/>
       <c r="C10" s="231"/>
@@ -4291,7 +4291,7 @@
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="227" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B11" s="228"/>
       <c r="C11" s="228"/>
@@ -4304,7 +4304,7 @@
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="233" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B12" s="234"/>
       <c r="C12" s="234"/>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="227" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B13" s="228"/>
       <c r="C13" s="228"/>
@@ -4331,13 +4331,13 @@
     <row r="14" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="221" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B15" s="222"/>
       <c r="C15" s="222"/>
       <c r="D15" s="223"/>
       <c r="E15" s="236" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F15" s="237"/>
     </row>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="60" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B19" s="61"/>
       <c r="C19" s="61"/>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B20" s="61"/>
       <c r="C20" s="61"/>
@@ -4409,7 +4409,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="230" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B21" s="231"/>
       <c r="C21" s="231"/>
@@ -4422,7 +4422,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="227" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B22" s="228"/>
       <c r="C22" s="228"/>
@@ -4435,7 +4435,7 @@
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="230" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="231"/>
       <c r="C23" s="231"/>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="206" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="B24" s="207"/>
       <c r="C24" s="207"/>
@@ -4461,7 +4461,7 @@
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="230" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="B25" s="231"/>
       <c r="C25" s="231"/>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="206" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B26" s="207"/>
       <c r="C26" s="207"/>
